--- a/data/mapping_berichte.xlsx
+++ b/data/mapping_berichte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\svmktgaccp01.tg.ch\data$\SK-Daten-und-Prozesse\stat\ogd\themenatlas_full\prepare_indikatoren\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13134CB-BA12-4E20-8DD8-6F1F7DD3CDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBBEB5C-4B6C-408E-81DD-D4FA48E79266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47895" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="312">
   <si>
     <t>topic</t>
   </si>
@@ -953,6 +953,9 @@
   </si>
   <si>
     <t>ds_0378</t>
+  </si>
+  <si>
+    <t>Eine Person</t>
   </si>
 </sst>
 </file>
@@ -1313,15 +1316,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O129"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="70.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="71.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="71.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1371,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1403,7 +1406,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1438,7 +1441,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1473,7 +1476,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1508,7 +1511,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1543,7 +1546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1578,7 +1581,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1613,7 +1616,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1648,7 +1651,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1683,7 +1686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1715,7 +1718,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1747,7 +1750,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1782,7 +1785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1817,7 +1820,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1852,7 +1855,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1884,7 +1887,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1916,7 +1919,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -1951,7 +1954,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>58</v>
       </c>
@@ -1986,7 +1989,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -2021,7 +2024,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -2056,7 +2059,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -2091,7 +2094,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -2126,7 +2129,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -2161,7 +2164,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -2190,7 +2193,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -2216,7 +2219,7 @@
         <v>79</v>
       </c>
       <c r="L26" t="s">
-        <v>65</v>
+        <v>311</v>
       </c>
       <c r="M26" t="b">
         <v>1</v>
@@ -2228,7 +2231,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>80</v>
       </c>
@@ -2257,7 +2260,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -2292,7 +2295,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -2327,7 +2330,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>80</v>
       </c>
@@ -2362,7 +2365,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>80</v>
       </c>
@@ -2397,7 +2400,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>80</v>
       </c>
@@ -2432,7 +2435,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -2464,7 +2467,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -2496,7 +2499,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2531,7 +2534,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -2566,7 +2569,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -2601,7 +2604,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -2636,7 +2639,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>80</v>
       </c>
@@ -2665,7 +2668,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>80</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -2729,7 +2732,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -2758,7 +2761,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>80</v>
       </c>
@@ -2790,7 +2793,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>80</v>
       </c>
@@ -2822,7 +2825,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>128</v>
       </c>
@@ -2854,7 +2857,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>128</v>
       </c>
@@ -2889,7 +2892,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>128</v>
       </c>
@@ -2924,7 +2927,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>128</v>
       </c>
@@ -2959,7 +2962,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>128</v>
       </c>
@@ -2994,7 +2997,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>128</v>
       </c>
@@ -3029,7 +3032,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>128</v>
       </c>
@@ -3058,7 +3061,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>128</v>
       </c>
@@ -3093,7 +3096,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>128</v>
       </c>
@@ -3122,7 +3125,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>128</v>
       </c>
@@ -3154,7 +3157,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>128</v>
       </c>
@@ -3186,7 +3189,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>128</v>
       </c>
@@ -3218,7 +3221,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>128</v>
       </c>
@@ -3253,7 +3256,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>128</v>
       </c>
@@ -3288,7 +3291,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>128</v>
       </c>
@@ -3323,7 +3326,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>128</v>
       </c>
@@ -3358,7 +3361,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>128</v>
       </c>
@@ -3393,7 +3396,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -3428,7 +3431,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>128</v>
       </c>
@@ -3463,7 +3466,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>128</v>
       </c>
@@ -3498,7 +3501,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>128</v>
       </c>
@@ -3533,7 +3536,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>128</v>
       </c>
@@ -3565,7 +3568,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>128</v>
       </c>
@@ -3591,7 +3594,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>128</v>
       </c>
@@ -3623,7 +3626,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>128</v>
       </c>
@@ -3655,7 +3658,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>199</v>
       </c>
@@ -3687,7 +3690,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>199</v>
       </c>
@@ -3719,7 +3722,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>199</v>
       </c>
@@ -3751,7 +3754,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>199</v>
       </c>
@@ -3783,7 +3786,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>199</v>
       </c>
@@ -3815,7 +3818,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -3847,7 +3850,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>199</v>
       </c>
@@ -3879,7 +3882,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>199</v>
       </c>
@@ -3911,7 +3914,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>199</v>
       </c>
@@ -3943,7 +3946,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>19</v>
       </c>
@@ -3978,7 +3981,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>19</v>
       </c>
@@ -4013,7 +4016,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>19</v>
       </c>
@@ -4048,7 +4051,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>19</v>
       </c>
@@ -4083,7 +4086,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>19</v>
       </c>
@@ -4118,7 +4121,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>19</v>
       </c>
@@ -4153,7 +4156,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>19</v>
       </c>
@@ -4188,7 +4191,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>19</v>
       </c>
@@ -4223,7 +4226,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>19</v>
       </c>
@@ -4258,7 +4261,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>19</v>
       </c>
@@ -4290,7 +4293,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>19</v>
       </c>
@@ -4325,7 +4328,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>19</v>
       </c>
@@ -4360,7 +4363,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>19</v>
       </c>
@@ -4395,7 +4398,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>19</v>
       </c>
@@ -4430,7 +4433,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>19</v>
       </c>
@@ -4465,7 +4468,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -4500,7 +4503,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>19</v>
       </c>
@@ -4535,7 +4538,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -4570,7 +4573,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>19</v>
       </c>
@@ -4602,7 +4605,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>19</v>
       </c>
@@ -4637,7 +4640,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>19</v>
       </c>
@@ -4672,7 +4675,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>19</v>
       </c>
@@ -4707,7 +4710,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -4739,7 +4742,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -4774,7 +4777,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -4809,7 +4812,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -4844,7 +4847,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -4879,7 +4882,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>19</v>
       </c>
@@ -4914,7 +4917,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>19</v>
       </c>
@@ -4949,7 +4952,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>19</v>
       </c>
@@ -4981,7 +4984,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>19</v>
       </c>
@@ -5016,7 +5019,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>19</v>
       </c>
@@ -5051,7 +5054,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>19</v>
       </c>
@@ -5086,7 +5089,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>19</v>
       </c>
@@ -5121,7 +5124,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>19</v>
       </c>
@@ -5156,7 +5159,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>268</v>
       </c>
@@ -5188,7 +5191,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>268</v>
       </c>
@@ -5220,7 +5223,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>268</v>
       </c>
@@ -5252,7 +5255,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>268</v>
       </c>
@@ -5281,7 +5284,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>268</v>
       </c>
@@ -5310,7 +5313,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>280</v>
       </c>
@@ -5339,7 +5342,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>280</v>
       </c>
@@ -5371,7 +5374,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>280</v>
       </c>
@@ -5406,7 +5409,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>280</v>
       </c>
@@ -5441,7 +5444,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>280</v>
       </c>
@@ -5476,7 +5479,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>280</v>
       </c>
@@ -5505,7 +5508,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>280</v>
       </c>
@@ -5537,7 +5540,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>280</v>
       </c>
@@ -5572,7 +5575,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>280</v>
       </c>
@@ -5607,7 +5610,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>280</v>
       </c>
@@ -5642,7 +5645,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>280</v>
       </c>
